--- a/polls/019_national_policy_reforms_poll--polls.xlsx
+++ b/polls/019_national_policy_reforms_poll--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>very_confident</t>
+          <t>very confident</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>somewhat_confident</t>
+          <t>somewhat confident</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>not_confident</t>
+          <t>not confident</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0_18</t>
+          <t>0 18</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>75_plus</t>
+          <t>75 plus</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>under_10000</t>
+          <t>under 10000</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>100000_plus</t>
+          <t>100000 plus</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>less_than_high_school</t>
+          <t>less than high school</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>high_school</t>
+          <t>high school</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>bachelor_degree</t>
+          <t>bachelor degree</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>masters_degree</t>
+          <t>masters degree</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>doctoral_degree</t>
+          <t>doctoral degree</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>prefer_not_to_answer</t>
+          <t>prefer not to answer</t>
         </is>
       </c>
     </row>
